--- a/xtb/HistoriaTransakcji.xlsx
+++ b/xtb/HistoriaTransakcji.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d98d39ada2f13ae1/Desktop/Foldery/Finanse osobiste/portfolio-management/xtb/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natal\Desktop\Codes\python\portfolio-management\xtb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_2B5928CF928B565EB1717DD2576050B07B63F60C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A274607E-AE76-4A74-89E1-54ADD413AAFB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D3CB7A-FBEF-4371-B843-CB52AA447FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transactions" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="30">
   <si>
     <t>ticker</t>
   </si>
@@ -98,6 +98,18 @@
   </si>
   <si>
     <t>timestamp</t>
+  </si>
+  <si>
+    <t>2026-05-11T16:07:00</t>
+  </si>
+  <si>
+    <t>2026-06-12T14:18:00</t>
+  </si>
+  <si>
+    <t>2026-05-11T16:31:00</t>
+  </si>
+  <si>
+    <t>2026-06-12T13:41:00</t>
   </si>
 </sst>
 </file>
@@ -452,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="20" customWidth="1"/>
@@ -593,25 +605,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>1.9616</v>
+        <v>3.6387</v>
       </c>
       <c r="E6">
-        <v>229.37</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4.2601000000000004</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -619,25 +631,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>11.824199999999999</v>
+        <v>6.0006000000000004</v>
       </c>
       <c r="E7">
-        <v>230.6</v>
+        <v>117.09</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>4.2694000000000001</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -651,13 +663,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>3.4796999999999998</v>
+        <v>1.9616</v>
       </c>
       <c r="E8">
-        <v>229.89</v>
+        <v>229.37</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -677,13 +689,13 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D9">
-        <v>3.0905</v>
+        <v>11.824199999999999</v>
       </c>
       <c r="E9">
-        <v>226.5</v>
+        <v>230.6</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -697,25 +709,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>0.62749999999999995</v>
+        <v>3.4796999999999998</v>
       </c>
       <c r="E10">
-        <v>93.27</v>
+        <v>229.89</v>
       </c>
       <c r="F10">
-        <v>4.2350000000000003</v>
+        <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -723,25 +735,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D11">
-        <v>17.255400000000002</v>
+        <v>3.0905</v>
       </c>
       <c r="E11">
-        <v>94.22</v>
+        <v>226.5</v>
       </c>
       <c r="F11">
-        <v>4.2343999999999999</v>
+        <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
@@ -755,21 +767,125 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <v>0.62749999999999995</v>
+      </c>
+      <c r="E12">
+        <v>93.27</v>
+      </c>
+      <c r="F12">
+        <v>4.2350000000000003</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>17.255400000000002</v>
+      </c>
+      <c r="E13">
+        <v>94.22</v>
+      </c>
+      <c r="F13">
+        <v>4.2343999999999999</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
         <v>16</v>
       </c>
-      <c r="D12">
+      <c r="D14">
         <v>17.876000000000001</v>
       </c>
-      <c r="E12">
+      <c r="E14">
         <v>94.3</v>
       </c>
-      <c r="F12">
+      <c r="F14">
         <v>4.2874999999999996</v>
       </c>
-      <c r="G12" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15">
+        <v>4.6383999999999999</v>
+      </c>
+      <c r="E15">
+        <v>101.3</v>
+      </c>
+      <c r="F15">
+        <v>4.2602000000000002</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16">
+        <v>6.7718999999999996</v>
+      </c>
+      <c r="E16">
+        <v>103.78</v>
+      </c>
+      <c r="F16">
+        <v>4.2686000000000002</v>
+      </c>
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s">
         <v>11</v>
       </c>
     </row>

--- a/xtb/HistoriaTransakcji.xlsx
+++ b/xtb/HistoriaTransakcji.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natal\Desktop\Codes\python\portfolio-management\xtb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D3CB7A-FBEF-4371-B843-CB52AA447FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82ED1D6-8407-4BE0-B0BF-8FEFB86D7541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transactions" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="32">
   <si>
     <t>ticker</t>
   </si>
@@ -110,6 +110,12 @@
   </si>
   <si>
     <t>2026-06-12T13:41:00</t>
+  </si>
+  <si>
+    <t>2026-06-22T13:05:00</t>
+  </si>
+  <si>
+    <t>2026-06-23T12:30:00</t>
   </si>
 </sst>
 </file>
@@ -464,13 +470,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -525,7 +531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -551,7 +557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -577,7 +583,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -603,7 +609,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -629,7 +635,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -655,33 +661,33 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>1.9616</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>229.37</v>
+        <v>118.17</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>4.2904999999999998</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -689,13 +695,13 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9">
-        <v>11.824199999999999</v>
+        <v>1.9616</v>
       </c>
       <c r="E9">
-        <v>230.6</v>
+        <v>229.37</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -707,7 +713,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -715,13 +721,13 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10">
-        <v>3.4796999999999998</v>
+        <v>11.824199999999999</v>
       </c>
       <c r="E10">
-        <v>229.89</v>
+        <v>230.6</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -733,7 +739,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -741,13 +747,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11">
-        <v>3.0905</v>
+        <v>3.4796999999999998</v>
       </c>
       <c r="E11">
-        <v>226.5</v>
+        <v>229.89</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -759,33 +765,33 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D12">
-        <v>0.62749999999999995</v>
+        <v>3.0905</v>
       </c>
       <c r="E12">
-        <v>93.27</v>
+        <v>226.5</v>
       </c>
       <c r="F12">
-        <v>4.2350000000000003</v>
+        <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -793,16 +799,16 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13">
-        <v>17.255400000000002</v>
+        <v>0.62749999999999995</v>
       </c>
       <c r="E13">
-        <v>94.22</v>
+        <v>93.27</v>
       </c>
       <c r="F13">
-        <v>4.2343999999999999</v>
+        <v>4.2350000000000003</v>
       </c>
       <c r="G13" t="s">
         <v>10</v>
@@ -811,7 +817,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -819,16 +825,16 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14">
-        <v>17.876000000000001</v>
+        <v>17.255400000000002</v>
       </c>
       <c r="E14">
-        <v>94.3</v>
+        <v>94.22</v>
       </c>
       <c r="F14">
-        <v>4.2874999999999996</v>
+        <v>4.2343999999999999</v>
       </c>
       <c r="G14" t="s">
         <v>10</v>
@@ -837,7 +843,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -845,16 +851,16 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D15">
-        <v>4.6383999999999999</v>
+        <v>17.876000000000001</v>
       </c>
       <c r="E15">
-        <v>101.3</v>
+        <v>94.3</v>
       </c>
       <c r="F15">
-        <v>4.2602000000000002</v>
+        <v>4.2874999999999996</v>
       </c>
       <c r="G15" t="s">
         <v>10</v>
@@ -863,7 +869,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -871,21 +877,73 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16">
+        <v>4.6383999999999999</v>
+      </c>
+      <c r="E16">
+        <v>101.3</v>
+      </c>
+      <c r="F16">
+        <v>4.2602000000000002</v>
+      </c>
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
         <v>29</v>
       </c>
-      <c r="D16">
+      <c r="D17">
         <v>6.7718999999999996</v>
       </c>
-      <c r="E16">
+      <c r="E17">
         <v>103.78</v>
       </c>
-      <c r="F16">
+      <c r="F17">
         <v>4.2686000000000002</v>
       </c>
-      <c r="G16" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18">
+        <v>14.067299999999999</v>
+      </c>
+      <c r="E18">
+        <v>104.6</v>
+      </c>
+      <c r="F18">
+        <v>4.3061999999999996</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s">
         <v>11</v>
       </c>
     </row>

--- a/xtb/HistoriaTransakcji.xlsx
+++ b/xtb/HistoriaTransakcji.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natal\Desktop\Codes\python\portfolio-management\xtb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82ED1D6-8407-4BE0-B0BF-8FEFB86D7541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F88E36B-1D20-4A3E-8EE2-92A242C0770D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transactions" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Transactions!$A$1:$I$30</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="36">
   <si>
     <t>ticker</t>
   </si>
@@ -116,6 +119,18 @@
   </si>
   <si>
     <t>2026-06-23T12:30:00</t>
+  </si>
+  <si>
+    <t>SELL</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:10:00</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:09:00</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:08:00</t>
   </si>
 </sst>
 </file>
@@ -470,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="9" width="20" customWidth="1"/>
@@ -947,7 +962,632 @@
         <v>11</v>
       </c>
     </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="E19">
+        <v>115.39</v>
+      </c>
+      <c r="F19">
+        <v>4.2835999999999999</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>115.4</v>
+      </c>
+      <c r="F20">
+        <v>4.2835999999999999</v>
+      </c>
+      <c r="G20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21">
+        <v>5.5880000000000001</v>
+      </c>
+      <c r="E21">
+        <v>115.41</v>
+      </c>
+      <c r="F21">
+        <v>4.2835999999999999</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22">
+        <v>6.0006000000000004</v>
+      </c>
+      <c r="E22">
+        <v>115.41</v>
+      </c>
+      <c r="F22">
+        <v>4.2835999999999999</v>
+      </c>
+      <c r="G22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23">
+        <v>3.6387</v>
+      </c>
+      <c r="E23">
+        <v>115.41</v>
+      </c>
+      <c r="F23">
+        <v>4.2835999999999999</v>
+      </c>
+      <c r="G23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24">
+        <v>1.9298999999999999</v>
+      </c>
+      <c r="E24">
+        <v>115.41</v>
+      </c>
+      <c r="F24">
+        <v>4.2835999999999999</v>
+      </c>
+      <c r="G24" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25">
+        <v>7.8428000000000004</v>
+      </c>
+      <c r="E25">
+        <v>115.41</v>
+      </c>
+      <c r="F25">
+        <v>4.2835999999999999</v>
+      </c>
+      <c r="G25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26">
+        <v>6.1760000000000002</v>
+      </c>
+      <c r="E26">
+        <v>115.41</v>
+      </c>
+      <c r="F26">
+        <v>4.2835999999999999</v>
+      </c>
+      <c r="G26" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="E27">
+        <v>115.23</v>
+      </c>
+      <c r="F27">
+        <v>4.2835999999999999</v>
+      </c>
+      <c r="G27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="E28">
+        <v>115.24</v>
+      </c>
+      <c r="F28">
+        <v>4.2836999999999996</v>
+      </c>
+      <c r="G28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="E29">
+        <v>115.26</v>
+      </c>
+      <c r="F29">
+        <v>4.2836999999999996</v>
+      </c>
+      <c r="G29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30">
+        <v>0.34920000000000001</v>
+      </c>
+      <c r="E30">
+        <v>115.26</v>
+      </c>
+      <c r="F30">
+        <v>4.2836999999999996</v>
+      </c>
+      <c r="G30" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31">
+        <v>3.0905</v>
+      </c>
+      <c r="E31">
+        <v>230.2</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32">
+        <v>3.4796999999999998</v>
+      </c>
+      <c r="E32">
+        <v>230.2</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33">
+        <v>11.824199999999999</v>
+      </c>
+      <c r="E33">
+        <v>230.2</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34">
+        <v>1.6055999999999999</v>
+      </c>
+      <c r="E34">
+        <v>230.2</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="E35">
+        <v>230.2</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36">
+        <v>14.067299999999999</v>
+      </c>
+      <c r="E36">
+        <v>105.6</v>
+      </c>
+      <c r="F36">
+        <v>4.2838000000000003</v>
+      </c>
+      <c r="G36" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37">
+        <v>6.7718999999999996</v>
+      </c>
+      <c r="E37">
+        <v>105.6</v>
+      </c>
+      <c r="F37">
+        <v>4.2838000000000003</v>
+      </c>
+      <c r="G37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38">
+        <v>4.6383999999999999</v>
+      </c>
+      <c r="E38">
+        <v>105.6</v>
+      </c>
+      <c r="F38">
+        <v>4.2838000000000003</v>
+      </c>
+      <c r="G38" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39">
+        <v>17.876000000000001</v>
+      </c>
+      <c r="E39">
+        <v>105.6</v>
+      </c>
+      <c r="F39">
+        <v>4.2838000000000003</v>
+      </c>
+      <c r="G39" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40">
+        <v>17.255400000000002</v>
+      </c>
+      <c r="E40">
+        <v>105.6</v>
+      </c>
+      <c r="F40">
+        <v>4.2838000000000003</v>
+      </c>
+      <c r="G40" t="s">
+        <v>10</v>
+      </c>
+      <c r="H40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="E41">
+        <v>105.6</v>
+      </c>
+      <c r="F41">
+        <v>4.2838000000000003</v>
+      </c>
+      <c r="G41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42">
+        <v>0.23649999999999999</v>
+      </c>
+      <c r="E42">
+        <v>105.6</v>
+      </c>
+      <c r="F42">
+        <v>4.2838000000000003</v>
+      </c>
+      <c r="G42" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:I30" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>